--- a/reports/2025-12-14/summary_daily.xlsx
+++ b/reports/2025-12-14/summary_daily.xlsx
@@ -413,11 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,97 +439,197 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>16548.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Net Total Sales</t>
+          <t>BEER</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3009.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GST 5%</t>
+          <t>COOLCIDER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1545.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PST 7%</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>235.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LIQ TAX 10%</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>111.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total taxes</t>
+          <t>Returns</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total Sales</t>
+          <t>Rewards</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-410</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>SPIRITS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>4660.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Customer count</t>
+          <t>WINE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>530.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>WINE RED</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2671.68</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WINE WHITE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2019.53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net Total Sales</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>14373.68</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GST 5%</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>726.5599999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PST 7%</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LIQ TAX 10%</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1444.41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total taxes</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2175.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Total Sales</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>16548.69</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>738.97</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Customer count</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Average Sale</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
+      <c r="B21" t="n">
+        <v>36.29717171717171</v>
       </c>
     </row>
   </sheetData>
